--- a/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès arrive au square. Il y a des bancs. Le vent sent l'herbe. Maman lui montre un espace. C'est le bac à sable. Maman dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Inès va au bac. Elle reste dans l'espace montré. Maman s'assoit. Maman voit Inès. L'adulte voit. Parce qu'Inès reste là, maman la voit. Inès verse le sable. Le sable est frais. Ses mains sont occupées. Elle fait un gâteau. Maman dit : je te vois. Inès sourit. Elle reste dans l'espace montré. Les pieds restent dans le bac.</t>
+          <t>Inès arrive au square. Il y a des bancs. Le vent sent l'herbe. Maman lui montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Inès va au bac. Elle reste dans l'espace montré. Maman s'assoit. Maman voit Inès. L'adulte voit. Parce qu'Inès reste là, maman la voit. Inès verse le sable. Le sable est frais. Ses mains sont occupées. Elle fait un gâteau. Je te vois. Inès sourit. Elle reste dans l'espace montré. Les pieds restent dans le bac.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès arrive au square. Il y a des bancs. Le vent sent l'herbe. Maman lui montre un espace. C'est le bac à sable.
+maman|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
+narrateur|Inès va au bac. Elle reste dans l'espace montré. Maman s'assoit. Maman voit Inès. L'adulte voit. Parce qu'Inès reste là, maman la voit. Inès verse le sable. Le sable est frais. Ses mains sont occupées. Elle fait un gâteau.
+maman|Je te vois.
+narrateur|Inès sourit. Elle reste dans l'espace montré. Les pieds restent dans le bac.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Inès joue au square. Où joue-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès est restée dans l'espace montré. Maman, l'adulte, la voyait.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Inès secoue ses mains. Maman range le seau. Ils rentrent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Inès sourit. Elle reste dans l'espace montré. Les pieds restent dans le bac.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Inès joue au square. Où joue-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Inès est restée dans l'espace montré. Maman, l'adulte, la voyait.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Inès secoue ses mains. Maman range le seau. Ils rentrent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inès reste dans l'espace montré</t>
+          <t>La menthe de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une feuille de menthe tremble. Nina fait un gâteau de sable au square, dans l'espace montré par maman.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Inès arrive au square. Il y a des bancs. Le vent sent l'herbe. Maman lui montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Inès va au bac. Elle reste dans l'espace montré. Maman s'assoit. Maman voit Inès. L'adulte voit. Parce qu'Inès reste là, maman la voit. Inès verse le sable. Le sable est frais. Ses mains sont occupées. Elle fait un gâteau. Je te vois. Inès sourit. Elle reste dans l'espace montré. Les pieds restent dans le bac.</t>
+          <t>Une feuille de menthe tremble dans le vent. Elle est dans une jardinière verte. Le banc du square est chaud. Le vent sent l'herbe et la menthe. Un oiseau picore une miette. La miette est petite et sèche. Tu as senti la menthe, Nina ? Ça pique le nez. Oui. C'est la menthe. Nina touche une feuille. Elle est fraîche et un peu collante. Elle est froide. Un peu, oui. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Nina va au bac. Elle reste dans l'espace montré. Maman s'assoit. Le bois du banc est chaud. Maman voit Nina. L'adulte voit. Parce que Nina reste là, maman la voit. Nina verse le sable. Le sable est frais. Il est frais, maman. Oui. Comme la menthe. Nina fait un gâteau. Ses mains sont occupées. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Les pieds restent dans le bac. Nina tasse encore le sable. Elle retourne le seau. Le gâteau de sable tient un peu. Un gâteau à la menthe. Presque. Tu as fait du bon travail. Nina pose une feuille à côté. La feuille sent fort. On en met une sur le gâteau ? Oui. Nina pose la feuille tout doux. Le gâteau a une petite feuille verte. Beau gâteau. Nina sourit. Elle reste dans l'espace montré. L'oiseau picore encore. La jardinière verte brille un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,11 +1324,61 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Inès arrive au square. Il y a des bancs. Le vent sent l'herbe. Maman lui montre un espace. C'est le bac à sable.
-maman|Tu joues ici. C'est l'espace montré. Ici, l'adulte voit.
-narrateur|Inès va au bac. Elle reste dans l'espace montré. Maman s'assoit. Maman voit Inès. L'adulte voit. Parce qu'Inès reste là, maman la voit. Inès verse le sable. Le sable est frais. Ses mains sont occupées. Elle fait un gâteau.
+          <t>narrateur|Une feuille de menthe tremble dans le vent.
+narrateur|Elle est dans une jardinière verte.
+narrateur|Le banc du square est chaud.
+narrateur|Le vent sent l'herbe et la menthe.
+narrateur|Un oiseau picore une miette.
+narrateur|La miette est petite et sèche.
+maman|Tu as senti la menthe, Nina ?
+enfant-f|Ça pique le nez.
+maman|Oui.
+maman|C'est la menthe.
+narrateur|Nina touche une feuille.
+narrateur|Elle est fraîche et un peu collante.
+enfant-f|Elle est froide.
+maman|Un peu, oui.
+narrateur|En ce moment, maman montre un espace.
+narrateur|C'est le bac à sable.
+maman|Tu joues ici.
+maman|C'est l'espace montré.
+maman|Ici, l'adulte voit.
+narrateur|Nina va au bac.
+narrateur|Elle reste dans l'espace montré.
+narrateur|Maman s'assoit.
+narrateur|Le bois du banc est chaud.
+narrateur|Maman voit Nina.
+narrateur|L'adulte voit.
+narrateur|Parce que Nina reste là, maman la voit.
+narrateur|Nina verse le sable.
+narrateur|Le sable est frais.
+enfant-f|Il est frais, maman.
+maman|Oui.
+maman|Comme la menthe.
+narrateur|Nina fait un gâteau.
+narrateur|Ses mains sont occupées.
 maman|Je te vois.
-narrateur|Inès sourit. Elle reste dans l'espace montré. Les pieds restent dans le bac.</t>
+maman|Tu restes dans l'espace montré ?
+enfant-f|Oui.
+maman|Bravo.
+narrateur|Les pieds restent dans le bac.
+narrateur|Nina tasse encore le sable.
+narrateur|Elle retourne le seau.
+narrateur|Le gâteau de sable tient un peu.
+enfant-f|Un gâteau à la menthe.
+maman|Presque.
+maman|Tu as fait du bon travail.
+narrateur|Nina pose une feuille à côté.
+narrateur|La feuille sent fort.
+maman|On en met une sur le gâteau ?
+enfant-f|Oui.
+narrateur|Nina pose la feuille tout doux.
+narrateur|Le gâteau a une petite feuille verte.
+maman|Beau gâteau.
+narrateur|Nina sourit.
+narrateur|Elle reste dans l'espace montré.
+narrateur|L'oiseau picore encore.
+narrateur|La jardinière verte brille un peu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Inès joue au square. Où joue-t-elle ?</t>
+          <t>Nina joue au square. Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1566,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Inès joue au square. Où joue-t-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina joue au square.
+narrateur|Où joue-t-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1594,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès est restée dans l'espace montré. Maman, l'adulte, la voyait.</t>
+          <t>Nina est restée dans l'espace montré. Maman, l'adulte, la voyait. L'adulte voit. Tu as joué dans l'espace montré ? Oui, maman. Bravo. Je te voyais. Le gâteau de sable est encore là. La menthe tremble encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1738,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Inès est restée dans l'espace montré. Maman, l'adulte, la voyait.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina est restée dans l'espace montré.
+narrateur|Maman, l'adulte, la voyait.
+narrateur|L'adulte voit.
+maman|Tu as joué dans l'espace montré ?
+enfant-f|Oui, maman.
+maman|Bravo.
+maman|Je te voyais.
+narrateur|Le gâteau de sable est encore là.
+narrateur|La menthe tremble encore.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Inès secoue ses mains. Maman range le seau. Ils rentrent.</t>
+          <t>Nina secoue ses mains. Le sable tombe tout doux. Il fait un petit bruit fin. Maman range le seau. Le seau a du sable au fond. Tu as fini le gâteau ? Oui. On rentre. Tu es restée dans l'espace montré. L'adulte voit. Oui. Bravo, Nina. Nina sent encore la menthe sur le doigt. Elle sent aussi un peu le sable. Le banc reste chaud, vide. L'oiseau s'envole, tout léger.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1913,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Inès secoue ses mains. Maman range le seau. Ils rentrent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina secoue ses mains.
+narrateur|Le sable tombe tout doux.
+narrateur|Il fait un petit bruit fin.
+narrateur|Maman range le seau.
+narrateur|Le seau a du sable au fond.
+maman|Tu as fini le gâteau ?
+enfant-f|Oui.
+maman|On rentre.
+maman|Tu es restée dans l'espace montré.
+enfant-f|L'adulte voit.
+maman|Oui.
+maman|Bravo, Nina.
+narrateur|Nina sent encore la menthe sur le doigt.
+narrateur|Elle sent aussi un peu le sable.
+narrateur|Le banc reste chaud, vide.
+narrateur|L'oiseau s'envole, tout léger.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La feuille de menthe tremble encore. J'ai fait un gâteau. Oui. Dans l'espace montré. Bravo, Nina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2095,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La feuille de menthe tremble encore.
+enfant-f|J'ai fait un gâteau.
+maman|Oui.
+maman|Dans l'espace montré.
+maman|Bravo, Nina.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2159,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une feuille de menthe tremble dans le vent. Elle est dans une jardinière verte. Le banc du square est chaud. Le vent sent l'herbe et la menthe. Un oiseau picore une miette. La miette est petite et sèche. Tu as senti la menthe, Nina ? Ça pique le nez. Oui. C'est la menthe. Nina touche une feuille. Elle est fraîche et un peu collante. Elle est froide. Un peu, oui. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Nina va au bac. Elle reste dans l'espace montré. Maman s'assoit. Le bois du banc est chaud. Maman voit Nina. L'adulte voit. Parce que Nina reste là, maman la voit. Nina verse le sable. Le sable est frais. Il est frais, maman. Oui. Comme la menthe. Nina fait un gâteau. Ses mains sont occupées. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Les pieds restent dans le bac. Nina tasse encore le sable. Elle retourne le seau. Le gâteau de sable tient un peu. Un gâteau à la menthe. Presque. Tu as fait du bon travail. Nina pose une feuille à côté. La feuille sent fort. On en met une sur le gâteau ? Oui. Nina pose la feuille tout doux. Le gâteau a une petite feuille verte. Beau gâteau. Nina sourit. Elle reste dans l'espace montré. L'oiseau picore encore. La jardinière verte brille un peu.</t>
+          <t>Une feuille de menthe tremble dans le vent. Elle est dans une jardinière verte. Le banc du square est chaud. Le vent sent l'herbe et la menthe. Un oiseau picore une miette. La miette est petite et sèche. Tu as senti la menthe, Nina ? Ça pique le nez. Oui. C'est la menthe. Nina touche une feuille. Elle est fraîche et un peu collante. Elle est froide. Un peu, oui. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Nina va au bac. Elle reste dans l'espace montré. Maman s'assoit. Le bois du banc est chaud. Maman voit Nina. L'adulte voit. Parce que Nina reste là, maman la voit. Nina verse le sable. Le sable est frais. Il est frais, maman. Oui. Comme la menthe. Nina fait un gâteau. Ses mains sont occupées. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Les pieds restent dans le bac. Nina tasse encore le sable. Elle retourne le seau. Le gâteau de sable tient un peu. Un gâteau à la menthe. Presque. Nina pose une feuille à côté. La feuille sent fort. On en met une sur le gâteau ? Oui. Nina pose la feuille tout doux. Le gâteau a une petite feuille verte. Beau gâteau. Nina sourit. Elle reste dans l'espace montré. L'oiseau picore encore. La jardinière verte brille un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès arrive au square. Il y a des bancs. Le vent sent l'herbe. Maman lui montre un &lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt;. C'est le bac à sable. Maman dit : tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Inès va au bac. Elle reste dans l'espace montré. Maman s'assoit. Maman voit Inès. L'adulte voit. Parce qu'Inès reste là, maman la voit. Inès verse le sable. Le sable est frais. Ses mains sont occupées. Elle fait un gâteau. Maman dit : je te vois. Inès sourit. Elle reste dans l'espace montré. Les pieds restent dans le bac.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une feuille de menthe tremble dans le vent. Elle est dans une jardinière verte. Le banc du square est chaud. Le vent sent l'herbe et la menthe. Un oiseau picore une miette. La miette est petite et sèche. Tu as senti la menthe, Nina ? Ça pique le nez. Oui. C'est la menthe. Nina touche une feuille. Elle est fraîche et un peu collante. Elle est froide. Un peu, oui. En ce moment, maman montre un espace. C'est le bac à sable. Tu joues ici. C'est l'espace montré. Ici, l'adulte voit. Nina va au bac. Elle reste dans l'espace montré. Maman s'assoit. Le bois du banc est chaud. Maman voit Nina. L'adulte voit. Parce que Nina reste là, maman la voit. Nina verse le sable. Le sable est frais. Il est frais, maman. Oui. Comme la menthe. Nina fait un gâteau. Ses mains sont occupées. Je te vois. Tu restes dans l'espace montré ? Oui. Bravo. Les pieds restent dans le bac. Nina tasse encore le sable. Elle retourne le seau. Le gâteau de sable tient un peu. Un gâteau à la menthe. Presque. Nina pose une feuille à côté. La feuille sent fort. On en met une sur le gâteau ? Oui. Nina pose la feuille tout doux. Le gâteau a une petite feuille verte. Beau gâteau. Nina sourit. Elle reste dans l'espace montré. L'oiseau picore encore. La jardinière verte brille un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1367,7 +1367,6 @@
 narrateur|Le gâteau de sable tient un peu.
 enfant-f|Un gâteau à la menthe.
 maman|Presque.
-maman|Tu as fait du bon travail.
 narrateur|Nina pose une feuille à côté.
 narrateur|La feuille sent fort.
 maman|On en met une sur le gâteau ?
@@ -1415,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Inès joue au square. Où joue-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina joue au square. Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1599,7 +1598,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès est restée dans l'&lt;emphasis level="moderate"&gt;espace&lt;/emphasis&gt; montré. Maman, l'adulte, la voyait.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina est restée dans l'espace montré. Maman, l'adulte, la voyait. L'adulte voit. Tu as joué dans l'espace montré ? Oui, maman. Bravo. Je te voyais. Le gâteau de sable est encore là. La menthe tremble encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1778,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Inès secoue ses &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;s. Maman range le seau. Ils rentrent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina secoue ses mains. Le sable tombe tout doux. Il fait un petit bruit fin. Maman range le seau. Le seau a du sable au fond. Tu as fini le gâteau ? Oui. On rentre. Tu es restée dans l'espace montré. L'adulte voit. Oui. Bravo, Nina. Nina sent encore la menthe sur le doigt. Elle sent aussi un peu le sable. Le banc reste chaud, vide. L'oiseau s'envole, tout léger.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1955,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La feuille de menthe tremble encore. J'ai fait un gâteau. Oui. Dans l'espace montré. Bravo, Nina. L'histoire est finie.</t>
+          <t>La feuille de menthe tremble encore. J'ai fait un gâteau. Oui. Dans l'espace montré. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La feuille de menthe tremble encore. J'ai fait un gâteau. Oui. Dans l'espace montré. Bravo, Nina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,8 +2098,7 @@
 enfant-f|J'ai fait un gâteau.
 maman|Oui.
 maman|Dans l'espace montré.
-maman|Bravo, Nina.
-narrateur|L'histoire est finie.</t>
+maman|Bravo, Nina.</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
+++ b/stories/arbres/ATOM-SEC.PAR.001-04.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>square, bac à sable</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Inès, maman</t>
+          <t>Nina, maman</t>
         </is>
       </c>
     </row>
